--- a/docs/26_Validation_Timing_Checklist.xlsx
+++ b/docs/26_Validation_Timing_Checklist.xlsx
@@ -16,7 +16,7 @@
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'How to Use'!$1:$2</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Gate Summary'!$4:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Build Checklist'!$A$4:$K$600</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Build Checklist'!$A$4:$L$600</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Build Checklist'!$4:$4</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'Build Checklist'!$A$1:$K$86</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Re-validation Log'!$A$4:$I$300</definedName>
@@ -33,7 +33,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="25">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -171,6 +171,12 @@
       <color rgb="FF404040"/>
       <sz val="10.5"/>
     </font>
+    <font>
+      <name val="Times New Roman"/>
+      <color rgb="FF0563C1"/>
+      <sz val="10"/>
+      <u val="single"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -265,7 +271,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -430,6 +436,18 @@
     </xf>
     <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -870,7 +888,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C37"/>
+  <dimension ref="A1:C38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -980,7 +998,7 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>When a row carries a Suite number, the column beside it says “Yes — check n”. Record that result in document 22 as well, on the Check Results tab, against the same check. Doc 22 is the formal record of the seventeen; this workbook is the working tick-list.</t>
+          <t>When a row carries a Suite number, the column beside it says “Yes — check n”. Record that result in document 22 as well, on the Check Results tab, against the same check. Doc 22 is the formal record of the seventeen; this workbook is the working tick-list. The Procedure column on the same row names the step-by-step document for that check in docs/validation/ — open it if you have not run the check before.</t>
         </is>
       </c>
     </row>
@@ -1179,6 +1197,18 @@
       <c r="C37" s="5" t="inlineStr">
         <is>
           <t>Development Checklist — the build tasks. Its phases map to the gates: G0 = Phases 0–1, G1 = 2, G2 = 3, G3 = 4, G4 = 5, G5 = 6, G6 = 7, G7 and G8 = 8, G9 = 9.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="30" customHeight="1">
+      <c r="B38" s="8" t="inlineStr">
+        <is>
+          <t>docs/validation/</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>One step-by-step procedure per suite check, V01 to V17, in .docx and .xlsx. The Procedure column on the Build Checklist names the one that covers each row.</t>
         </is>
       </c>
     </row>
@@ -1844,7 +1874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K600"/>
+  <dimension ref="A1:L600"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -1858,6 +1888,7 @@
     <col width="11" customWidth="1" min="9" max="9"/>
     <col width="11" customWidth="1" min="10" max="10"/>
     <col width="40" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -1870,7 +1901,7 @@
     <row r="2" ht="32" customHeight="1">
       <c r="A2" s="10" t="inlineStr">
         <is>
-          <t>The recording companion to document 25. Work down the gates in order and set Result on every row; the Gate Summary tab counts itself from this column. A row with a Suite number is also recorded in document 22 against the same check. A gate is PASSED when every row is Pass or N/A.</t>
+          <t>The recording companion to document 25. Work down the gates in order and set Result on every row; the Gate Summary tab counts itself from this column. A row with a Suite number is also recorded in document 22 against the same check. A gate is PASSED when every row is Pass or N/A. The Procedure column names the step-by-step document for that check in docs/validation/ — one file per check, V01 to V17.</t>
         </is>
       </c>
     </row>
@@ -1928,6 +1959,11 @@
       <c r="K4" s="34" t="inlineStr">
         <is>
           <t>Observed value / notes</t>
+        </is>
+      </c>
+      <c r="L4" s="34" t="inlineStr">
+        <is>
+          <t>Procedure</t>
         </is>
       </c>
     </row>
@@ -1946,7 +1982,8 @@
       <c r="H5" s="36" t="n"/>
       <c r="I5" s="36" t="n"/>
       <c r="J5" s="36" t="n"/>
-      <c r="K5" s="37" t="n"/>
+      <c r="K5" s="36" t="n"/>
+      <c r="L5" s="37" t="n"/>
     </row>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="38" t="inlineStr">
@@ -2083,7 +2120,8 @@
       <c r="H9" s="36" t="n"/>
       <c r="I9" s="36" t="n"/>
       <c r="J9" s="36" t="n"/>
-      <c r="K9" s="37" t="n"/>
+      <c r="K9" s="36" t="n"/>
+      <c r="L9" s="37" t="n"/>
     </row>
     <row r="10" ht="30" customHeight="1">
       <c r="A10" s="38" t="inlineStr">
@@ -2286,6 +2324,11 @@
       <c r="I14" s="43" t="n"/>
       <c r="J14" s="16" t="n"/>
       <c r="K14" s="15" t="n"/>
+      <c r="L14" s="59" t="inlineStr">
+        <is>
+          <t>V01</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="30" customHeight="1">
       <c r="A15" s="44" t="inlineStr">
@@ -2328,6 +2371,11 @@
       <c r="I15" s="50" t="n"/>
       <c r="J15" s="23" t="n"/>
       <c r="K15" s="22" t="n"/>
+      <c r="L15" s="60" t="inlineStr">
+        <is>
+          <t>V12</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="30" customHeight="1">
       <c r="A16" s="38" t="inlineStr">
@@ -2424,7 +2472,8 @@
       <c r="H18" s="36" t="n"/>
       <c r="I18" s="36" t="n"/>
       <c r="J18" s="36" t="n"/>
-      <c r="K18" s="37" t="n"/>
+      <c r="K18" s="36" t="n"/>
+      <c r="L18" s="37" t="n"/>
     </row>
     <row r="19" ht="30" customHeight="1">
       <c r="A19" s="38" t="inlineStr">
@@ -2507,6 +2556,11 @@
       <c r="I20" s="50" t="n"/>
       <c r="J20" s="23" t="n"/>
       <c r="K20" s="22" t="n"/>
+      <c r="L20" s="60" t="inlineStr">
+        <is>
+          <t>V02</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="30" customHeight="1">
       <c r="A21" s="38" t="inlineStr">
@@ -2589,6 +2643,11 @@
       <c r="I22" s="50" t="n"/>
       <c r="J22" s="23" t="n"/>
       <c r="K22" s="22" t="n"/>
+      <c r="L22" s="60" t="inlineStr">
+        <is>
+          <t>V05</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="30" customHeight="1">
       <c r="A23" s="38" t="inlineStr">
@@ -2685,7 +2744,8 @@
       <c r="H25" s="36" t="n"/>
       <c r="I25" s="36" t="n"/>
       <c r="J25" s="36" t="n"/>
-      <c r="K25" s="37" t="n"/>
+      <c r="K25" s="36" t="n"/>
+      <c r="L25" s="37" t="n"/>
     </row>
     <row r="26" ht="30" customHeight="1">
       <c r="A26" s="38" t="inlineStr">
@@ -2808,6 +2868,11 @@
       <c r="I28" s="43" t="n"/>
       <c r="J28" s="16" t="n"/>
       <c r="K28" s="15" t="n"/>
+      <c r="L28" s="59" t="inlineStr">
+        <is>
+          <t>V06</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="30" customHeight="1">
       <c r="A29" s="44" t="inlineStr">
@@ -2864,7 +2929,8 @@
       <c r="H30" s="36" t="n"/>
       <c r="I30" s="36" t="n"/>
       <c r="J30" s="36" t="n"/>
-      <c r="K30" s="37" t="n"/>
+      <c r="K30" s="36" t="n"/>
+      <c r="L30" s="37" t="n"/>
     </row>
     <row r="31" ht="30" customHeight="1">
       <c r="A31" s="38" t="inlineStr">
@@ -2949,6 +3015,11 @@
       <c r="I32" s="50" t="n"/>
       <c r="J32" s="23" t="n"/>
       <c r="K32" s="22" t="n"/>
+      <c r="L32" s="61" t="inlineStr">
+        <is>
+          <t>V03, V04</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="30" customHeight="1">
       <c r="A33" s="38" t="inlineStr">
@@ -2991,6 +3062,11 @@
       <c r="I33" s="43" t="n"/>
       <c r="J33" s="16" t="n"/>
       <c r="K33" s="15" t="n"/>
+      <c r="L33" s="59" t="inlineStr">
+        <is>
+          <t>V11</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="30" customHeight="1">
       <c r="A34" s="44" t="inlineStr">
@@ -3075,6 +3151,11 @@
       <c r="I35" s="43" t="n"/>
       <c r="J35" s="16" t="n"/>
       <c r="K35" s="15" t="n"/>
+      <c r="L35" s="62" t="inlineStr">
+        <is>
+          <t>V09, V10</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="30" customHeight="1">
       <c r="A36" s="44" t="inlineStr">
@@ -3199,6 +3280,11 @@
       <c r="I38" s="50" t="n"/>
       <c r="J38" s="23" t="n"/>
       <c r="K38" s="22" t="n"/>
+      <c r="L38" s="61" t="inlineStr">
+        <is>
+          <t>V13, V14</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="30" customHeight="1">
       <c r="A39" s="38" t="inlineStr">
@@ -3295,7 +3381,8 @@
       <c r="H41" s="36" t="n"/>
       <c r="I41" s="36" t="n"/>
       <c r="J41" s="36" t="n"/>
-      <c r="K41" s="37" t="n"/>
+      <c r="K41" s="36" t="n"/>
+      <c r="L41" s="37" t="n"/>
     </row>
     <row r="42" ht="30" customHeight="1">
       <c r="A42" s="38" t="inlineStr">
@@ -3338,6 +3425,11 @@
       <c r="I42" s="43" t="n"/>
       <c r="J42" s="16" t="n"/>
       <c r="K42" s="15" t="n"/>
+      <c r="L42" s="59" t="inlineStr">
+        <is>
+          <t>V01</t>
+        </is>
+      </c>
     </row>
     <row r="43" ht="30" customHeight="1">
       <c r="A43" s="44" t="inlineStr">
@@ -3380,6 +3472,11 @@
       <c r="I43" s="50" t="n"/>
       <c r="J43" s="23" t="n"/>
       <c r="K43" s="22" t="n"/>
+      <c r="L43" s="60" t="inlineStr">
+        <is>
+          <t>V02</t>
+        </is>
+      </c>
     </row>
     <row r="44" ht="30" customHeight="1">
       <c r="A44" s="38" t="inlineStr">
@@ -3422,6 +3519,11 @@
       <c r="I44" s="43" t="n"/>
       <c r="J44" s="16" t="n"/>
       <c r="K44" s="15" t="n"/>
+      <c r="L44" s="59" t="inlineStr">
+        <is>
+          <t>V03</t>
+        </is>
+      </c>
     </row>
     <row r="45" ht="30" customHeight="1">
       <c r="A45" s="44" t="inlineStr">
@@ -3464,6 +3566,11 @@
       <c r="I45" s="50" t="n"/>
       <c r="J45" s="23" t="n"/>
       <c r="K45" s="22" t="n"/>
+      <c r="L45" s="60" t="inlineStr">
+        <is>
+          <t>V04</t>
+        </is>
+      </c>
     </row>
     <row r="46" ht="30" customHeight="1">
       <c r="A46" s="38" t="inlineStr">
@@ -3506,6 +3613,11 @@
       <c r="I46" s="43" t="n"/>
       <c r="J46" s="16" t="n"/>
       <c r="K46" s="15" t="n"/>
+      <c r="L46" s="59" t="inlineStr">
+        <is>
+          <t>V05</t>
+        </is>
+      </c>
     </row>
     <row r="47" ht="30" customHeight="1">
       <c r="A47" s="44" t="inlineStr">
@@ -3548,6 +3660,11 @@
       <c r="I47" s="50" t="n"/>
       <c r="J47" s="23" t="n"/>
       <c r="K47" s="22" t="n"/>
+      <c r="L47" s="60" t="inlineStr">
+        <is>
+          <t>V06</t>
+        </is>
+      </c>
     </row>
     <row r="48" ht="30" customHeight="1">
       <c r="A48" s="38" t="inlineStr">
@@ -3590,6 +3707,11 @@
       <c r="I48" s="43" t="n"/>
       <c r="J48" s="16" t="n"/>
       <c r="K48" s="15" t="n"/>
+      <c r="L48" s="59" t="inlineStr">
+        <is>
+          <t>V09</t>
+        </is>
+      </c>
     </row>
     <row r="49" ht="30" customHeight="1">
       <c r="A49" s="44" t="inlineStr">
@@ -3632,6 +3754,11 @@
       <c r="I49" s="50" t="n"/>
       <c r="J49" s="23" t="n"/>
       <c r="K49" s="22" t="n"/>
+      <c r="L49" s="60" t="inlineStr">
+        <is>
+          <t>V10</t>
+        </is>
+      </c>
     </row>
     <row r="50" ht="30" customHeight="1">
       <c r="A50" s="38" t="inlineStr">
@@ -3674,6 +3801,11 @@
       <c r="I50" s="43" t="n"/>
       <c r="J50" s="16" t="n"/>
       <c r="K50" s="15" t="n"/>
+      <c r="L50" s="59" t="inlineStr">
+        <is>
+          <t>V11</t>
+        </is>
+      </c>
     </row>
     <row r="51" ht="30" customHeight="1">
       <c r="A51" s="44" t="inlineStr">
@@ -3716,6 +3848,11 @@
       <c r="I51" s="50" t="n"/>
       <c r="J51" s="23" t="n"/>
       <c r="K51" s="22" t="n"/>
+      <c r="L51" s="60" t="inlineStr">
+        <is>
+          <t>V12</t>
+        </is>
+      </c>
     </row>
     <row r="52" ht="30" customHeight="1">
       <c r="A52" s="38" t="inlineStr">
@@ -3758,6 +3895,11 @@
       <c r="I52" s="43" t="n"/>
       <c r="J52" s="16" t="n"/>
       <c r="K52" s="15" t="n"/>
+      <c r="L52" s="59" t="inlineStr">
+        <is>
+          <t>V13</t>
+        </is>
+      </c>
     </row>
     <row r="53" ht="30" customHeight="1">
       <c r="A53" s="44" t="inlineStr">
@@ -3800,6 +3942,11 @@
       <c r="I53" s="50" t="n"/>
       <c r="J53" s="23" t="n"/>
       <c r="K53" s="22" t="n"/>
+      <c r="L53" s="60" t="inlineStr">
+        <is>
+          <t>V14</t>
+        </is>
+      </c>
     </row>
     <row r="54" ht="30" customHeight="1">
       <c r="A54" s="38" t="inlineStr">
@@ -3856,7 +4003,8 @@
       <c r="H55" s="36" t="n"/>
       <c r="I55" s="36" t="n"/>
       <c r="J55" s="36" t="n"/>
-      <c r="K55" s="37" t="n"/>
+      <c r="K55" s="36" t="n"/>
+      <c r="L55" s="37" t="n"/>
     </row>
     <row r="56" ht="30" customHeight="1">
       <c r="A56" s="38" t="inlineStr">
@@ -3979,6 +4127,11 @@
       <c r="I58" s="43" t="n"/>
       <c r="J58" s="16" t="n"/>
       <c r="K58" s="15" t="n"/>
+      <c r="L58" s="59" t="inlineStr">
+        <is>
+          <t>V17</t>
+        </is>
+      </c>
     </row>
     <row r="59" ht="30" customHeight="1">
       <c r="A59" s="44" t="inlineStr">
@@ -4021,6 +4174,11 @@
       <c r="I59" s="50" t="n"/>
       <c r="J59" s="23" t="n"/>
       <c r="K59" s="22" t="n"/>
+      <c r="L59" s="60" t="inlineStr">
+        <is>
+          <t>V17</t>
+        </is>
+      </c>
     </row>
     <row r="60" ht="30" customHeight="1">
       <c r="A60" s="38" t="inlineStr">
@@ -4063,6 +4221,11 @@
       <c r="I60" s="43" t="n"/>
       <c r="J60" s="16" t="n"/>
       <c r="K60" s="15" t="n"/>
+      <c r="L60" s="59" t="inlineStr">
+        <is>
+          <t>V17</t>
+        </is>
+      </c>
     </row>
     <row r="61" ht="20" customHeight="1">
       <c r="A61" s="35" t="inlineStr">
@@ -4079,7 +4242,8 @@
       <c r="H61" s="36" t="n"/>
       <c r="I61" s="36" t="n"/>
       <c r="J61" s="36" t="n"/>
-      <c r="K61" s="37" t="n"/>
+      <c r="K61" s="36" t="n"/>
+      <c r="L61" s="37" t="n"/>
     </row>
     <row r="62" ht="30" customHeight="1">
       <c r="A62" s="38" t="inlineStr">
@@ -4162,6 +4326,11 @@
       <c r="I63" s="50" t="n"/>
       <c r="J63" s="23" t="n"/>
       <c r="K63" s="22" t="n"/>
+      <c r="L63" s="60" t="inlineStr">
+        <is>
+          <t>V07</t>
+        </is>
+      </c>
     </row>
     <row r="64" ht="30" customHeight="1">
       <c r="A64" s="38" t="inlineStr">
@@ -4246,6 +4415,11 @@
       <c r="I65" s="50" t="n"/>
       <c r="J65" s="23" t="n"/>
       <c r="K65" s="22" t="n"/>
+      <c r="L65" s="61" t="inlineStr">
+        <is>
+          <t>V08, V09, V10, V11</t>
+        </is>
+      </c>
     </row>
     <row r="66" ht="30" customHeight="1">
       <c r="A66" s="38" t="inlineStr">
@@ -4330,6 +4504,11 @@
       <c r="I67" s="50" t="n"/>
       <c r="J67" s="23" t="n"/>
       <c r="K67" s="22" t="n"/>
+      <c r="L67" s="61" t="inlineStr">
+        <is>
+          <t>V07, V08, V15</t>
+        </is>
+      </c>
     </row>
     <row r="68" ht="30" customHeight="1">
       <c r="A68" s="38" t="inlineStr">
@@ -4374,6 +4553,11 @@
       <c r="I68" s="43" t="n"/>
       <c r="J68" s="16" t="n"/>
       <c r="K68" s="15" t="n"/>
+      <c r="L68" s="62" t="inlineStr">
+        <is>
+          <t>V07, V08, V09</t>
+        </is>
+      </c>
     </row>
     <row r="69" ht="30" customHeight="1">
       <c r="A69" s="44" t="inlineStr">
@@ -4416,6 +4600,11 @@
       <c r="I69" s="50" t="n"/>
       <c r="J69" s="23" t="n"/>
       <c r="K69" s="22" t="n"/>
+      <c r="L69" s="60" t="inlineStr">
+        <is>
+          <t>V15</t>
+        </is>
+      </c>
     </row>
     <row r="70" ht="30" customHeight="1">
       <c r="A70" s="38" t="inlineStr">
@@ -4500,6 +4689,11 @@
       <c r="I71" s="50" t="n"/>
       <c r="J71" s="23" t="n"/>
       <c r="K71" s="22" t="n"/>
+      <c r="L71" s="61" t="inlineStr">
+        <is>
+          <t>V07, V08, V14</t>
+        </is>
+      </c>
     </row>
     <row r="72" ht="30" customHeight="1">
       <c r="A72" s="38" t="inlineStr">
@@ -4542,6 +4736,11 @@
       <c r="I72" s="43" t="n"/>
       <c r="J72" s="16" t="n"/>
       <c r="K72" s="15" t="n"/>
+      <c r="L72" s="59" t="inlineStr">
+        <is>
+          <t>V16</t>
+        </is>
+      </c>
     </row>
     <row r="73" ht="30" customHeight="1">
       <c r="A73" s="44" t="inlineStr">
@@ -4586,6 +4785,11 @@
       <c r="I73" s="50" t="n"/>
       <c r="J73" s="23" t="n"/>
       <c r="K73" s="22" t="n"/>
+      <c r="L73" s="61" t="inlineStr">
+        <is>
+          <t>V07, V08</t>
+        </is>
+      </c>
     </row>
     <row r="74" ht="30" customHeight="1">
       <c r="A74" s="38" t="inlineStr">
@@ -4628,6 +4832,11 @@
       <c r="I74" s="43" t="n"/>
       <c r="J74" s="16" t="n"/>
       <c r="K74" s="15" t="n"/>
+      <c r="L74" s="59" t="inlineStr">
+        <is>
+          <t>V08</t>
+        </is>
+      </c>
     </row>
     <row r="75" ht="20" customHeight="1">
       <c r="A75" s="35" t="inlineStr">
@@ -4644,7 +4853,8 @@
       <c r="H75" s="36" t="n"/>
       <c r="I75" s="36" t="n"/>
       <c r="J75" s="36" t="n"/>
-      <c r="K75" s="37" t="n"/>
+      <c r="K75" s="36" t="n"/>
+      <c r="L75" s="37" t="n"/>
     </row>
     <row r="76" ht="30" customHeight="1">
       <c r="A76" s="38" t="inlineStr">
@@ -4689,6 +4899,11 @@
       <c r="I76" s="43" t="n"/>
       <c r="J76" s="16" t="n"/>
       <c r="K76" s="15" t="n"/>
+      <c r="L76" s="62" t="inlineStr">
+        <is>
+          <t>V07, V08, V15, V16, V17</t>
+        </is>
+      </c>
     </row>
     <row r="77" ht="30" customHeight="1">
       <c r="A77" s="44" t="inlineStr">
@@ -4773,6 +4988,11 @@
       <c r="I78" s="43" t="n"/>
       <c r="J78" s="16" t="n"/>
       <c r="K78" s="15" t="n"/>
+      <c r="L78" s="62" t="inlineStr">
+        <is>
+          <t>V07, V08, V15, V16, V17</t>
+        </is>
+      </c>
     </row>
     <row r="79" ht="30" customHeight="1">
       <c r="A79" s="44" t="inlineStr">
@@ -4857,6 +5077,11 @@
       <c r="I80" s="43" t="n"/>
       <c r="J80" s="16" t="n"/>
       <c r="K80" s="15" t="n"/>
+      <c r="L80" s="62" t="inlineStr">
+        <is>
+          <t>V07, V08, V15, V16, V17</t>
+        </is>
+      </c>
     </row>
     <row r="81" ht="30" customHeight="1">
       <c r="A81" s="44" t="inlineStr">
@@ -4953,7 +5178,8 @@
       <c r="H83" s="36" t="n"/>
       <c r="I83" s="36" t="n"/>
       <c r="J83" s="36" t="n"/>
-      <c r="K83" s="37" t="n"/>
+      <c r="K83" s="36" t="n"/>
+      <c r="L83" s="37" t="n"/>
     </row>
     <row r="84" ht="30" customHeight="1">
       <c r="A84" s="38" t="inlineStr">
@@ -13300,20 +13526,20 @@
       <c r="K600" s="53" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:K600"/>
+  <autoFilter ref="A4:L600"/>
   <mergeCells count="12">
-    <mergeCell ref="A61:K61"/>
-    <mergeCell ref="A83:K83"/>
-    <mergeCell ref="A18:K18"/>
-    <mergeCell ref="A30:K30"/>
-    <mergeCell ref="A55:K55"/>
-    <mergeCell ref="A25:K25"/>
-    <mergeCell ref="A41:K41"/>
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A5:K5"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A75:K75"/>
-    <mergeCell ref="A9:K9"/>
+    <mergeCell ref="A25:L25"/>
+    <mergeCell ref="A41:L41"/>
+    <mergeCell ref="A75:L75"/>
+    <mergeCell ref="A18:L18"/>
+    <mergeCell ref="A9:L9"/>
+    <mergeCell ref="A55:L55"/>
+    <mergeCell ref="A83:L83"/>
+    <mergeCell ref="A30:L30"/>
+    <mergeCell ref="A2:L2"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A5:L5"/>
+    <mergeCell ref="A61:L61"/>
   </mergeCells>
   <conditionalFormatting sqref="H5:H600">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
@@ -13337,6 +13563,33 @@
       <formula1>"G0,G1,G2,G3,G4,G5,G6,G7,G8,G9"</formula1>
     </dataValidation>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L14" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L15" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L20" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L22" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L28" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L33" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L42" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L43" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L44" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L45" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L46" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L47" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L48" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L49" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L50" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L51" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L52" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L53" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L58" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L59" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L60" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L63" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L69" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L72" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L74" r:id="rId25"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>

--- a/docs/26_Validation_Timing_Checklist.xlsx
+++ b/docs/26_Validation_Timing_Checklist.xlsx
@@ -910,6 +910,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -917,6 +918,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6" ht="32" customHeight="1">
       <c r="B6" s="4" t="inlineStr">
         <is>
@@ -929,7 +931,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="18" customHeight="1">
+    <row r="7" ht="16" customHeight="1">
       <c r="B7" s="4" t="inlineStr">
         <is>
           <t>Build Checklist</t>
@@ -937,7 +939,7 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>Ten gates, G0 to G9, and 72 checks in build order. This is the tab you fill in.</t>
+          <t>Ten gates, G0 to G9, and 76 checks in build order. This is the tab you fill in.</t>
         </is>
       </c>
     </row>
@@ -953,7 +955,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="32" customHeight="1">
+    <row r="9" ht="29.5" customHeight="1">
       <c r="B9" s="4" t="inlineStr">
         <is>
           <t>Triggers</t>
@@ -961,7 +963,7 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>The nine events from document 25 Table 4.1, with what each requires. Reference only; the Re-validation Log reads from it.</t>
+          <t>The eleven events from document 25 Table 4.1, with what each requires. Reference only; the Re-validation Log reads from it.</t>
         </is>
       </c>
     </row>
@@ -972,6 +974,7 @@
         </is>
       </c>
     </row>
+    <row r="11"/>
     <row r="12" ht="30" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>1</v>
@@ -1029,6 +1032,7 @@
         </is>
       </c>
     </row>
+    <row r="18"/>
     <row r="19" ht="18" customHeight="1">
       <c r="B19" s="8" t="inlineStr">
         <is>
@@ -1084,6 +1088,7 @@
         </is>
       </c>
     </row>
+    <row r="24"/>
     <row r="25" ht="30" customHeight="1">
       <c r="A25" s="6" t="n">
         <v>1</v>
@@ -1121,6 +1126,7 @@
         </is>
       </c>
     </row>
+    <row r="29"/>
     <row r="30" ht="30" customHeight="1">
       <c r="A30" s="6" t="inlineStr">
         <is>
@@ -1164,6 +1170,7 @@
         </is>
       </c>
     </row>
+    <row r="34"/>
     <row r="35" ht="18" customHeight="1">
       <c r="B35" s="8" t="inlineStr">
         <is>
@@ -1874,7 +1881,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L600"/>
+  <dimension ref="A1:L604"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -1905,6 +1912,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="32" customHeight="1">
       <c r="A4" s="34" t="inlineStr">
         <is>
@@ -3108,7 +3116,7 @@
       <c r="J34" s="23" t="n"/>
       <c r="K34" s="22" t="n"/>
     </row>
-    <row r="35" ht="30" customHeight="1">
+    <row r="35" ht="70" customHeight="1">
       <c r="A35" s="38" t="inlineStr">
         <is>
           <t>G4</t>
@@ -3126,7 +3134,7 @@
       </c>
       <c r="D35" s="15" t="inlineStr">
         <is>
-          <t>2019 baseline query returns no rows; national series direction recorded</t>
+          <t>2019 baseline query returns no rows for any class, type and year; national series direction recorded</t>
         </is>
       </c>
       <c r="E35" s="40" t="inlineStr">
@@ -3237,7 +3245,7 @@
       <c r="J37" s="16" t="n"/>
       <c r="K37" s="15" t="n"/>
     </row>
-    <row r="38" ht="30" customHeight="1">
+    <row r="38" ht="70" customHeight="1">
       <c r="A38" s="44" t="inlineStr">
         <is>
           <t>G4</t>
@@ -3255,7 +3263,7 @@
       </c>
       <c r="D38" s="22" t="inlineStr">
         <is>
-          <t>Every item has a cohort year; Cumulative Cases % is exactly 1 at the lowest rank</t>
+          <t>Cohort Size by year sums to the DimItem row count; Cumulative Cases % is exactly 1 at the lowest rank</t>
         </is>
       </c>
       <c r="E38" s="47" t="inlineStr">
@@ -3666,7 +3674,7 @@
         </is>
       </c>
     </row>
-    <row r="48" ht="30" customHeight="1">
+    <row r="48" ht="70" customHeight="1">
       <c r="A48" s="38" t="inlineStr">
         <is>
           <t>G5</t>
@@ -3684,7 +3692,7 @@
       </c>
       <c r="D48" s="15" t="inlineStr">
         <is>
-          <t>2019 baseline returns a value for every combination</t>
+          <t>2019 baselines return a value for every class, type and year (V09 Parts 1 and 3)</t>
         </is>
       </c>
       <c r="E48" s="40" t="inlineStr">
@@ -3854,7 +3862,7 @@
         </is>
       </c>
     </row>
-    <row r="52" ht="30" customHeight="1">
+    <row r="52" ht="70" customHeight="1">
       <c r="A52" s="38" t="inlineStr">
         <is>
           <t>G5</t>
@@ -3872,7 +3880,7 @@
       </c>
       <c r="D52" s="15" t="inlineStr">
         <is>
-          <t>Every item has a cohort year</t>
+          <t>Cohort Size summed across CohortYear equals the DimItem row count</t>
         </is>
       </c>
       <c r="E52" s="40" t="inlineStr">
@@ -3901,7 +3909,7 @@
         </is>
       </c>
     </row>
-    <row r="53" ht="30" customHeight="1">
+    <row r="53" ht="70" customHeight="1">
       <c r="A53" s="44" t="inlineStr">
         <is>
           <t>G5</t>
@@ -3919,7 +3927,7 @@
       </c>
       <c r="D53" s="22" t="inlineStr">
         <is>
-          <t>Cumulative Cases % reaches exactly 100%</t>
+          <t>Cumulative Cases % is exactly 100% at the lowest rank, unfiltered and under each year and item type</t>
         </is>
       </c>
       <c r="E53" s="47" t="inlineStr">
@@ -3948,7 +3956,7 @@
         </is>
       </c>
     </row>
-    <row r="54" ht="30" customHeight="1">
+    <row r="54" ht="70" customHeight="1">
       <c r="A54" s="38" t="inlineStr">
         <is>
           <t>G5</t>
@@ -3966,7 +3974,7 @@
       </c>
       <c r="D54" s="15" t="inlineStr">
         <is>
-          <t>Reads INCOMPLETE — 5 not recorded, with zero Blocking failures</t>
+          <t>Reads INCOMPLETE — 5 not recorded, with zero Blocking failures (an Advisory failure adds “· n Advisory failing”)</t>
         </is>
       </c>
       <c r="E54" s="40" t="inlineStr">
@@ -4006,7 +4014,7 @@
       <c r="K55" s="36" t="n"/>
       <c r="L55" s="37" t="n"/>
     </row>
-    <row r="56" ht="30" customHeight="1">
+    <row r="56" ht="70" customHeight="1">
       <c r="A56" s="38" t="inlineStr">
         <is>
           <t>G6</t>
@@ -4024,7 +4032,7 @@
       </c>
       <c r="D56" s="15" t="inlineStr">
         <is>
-          <t>All four sources refresh: SQL Server and RefMappings.xlsx through the gateway</t>
+          <t>All four sources refresh: SQL Server and RefMappings.xlsx through the gateway, FRED and Census without it</t>
         </is>
       </c>
       <c r="E56" s="40" t="inlineStr">
@@ -4285,7 +4293,7 @@
       <c r="J62" s="16" t="n"/>
       <c r="K62" s="15" t="n"/>
     </row>
-    <row r="63" ht="30" customHeight="1">
+    <row r="63" ht="70" customHeight="1">
       <c r="A63" s="44" t="inlineStr">
         <is>
           <t>G7</t>
@@ -4303,7 +4311,7 @@
       </c>
       <c r="D63" s="22" t="inlineStr">
         <is>
-          <t>Dual-axis visual 1.6 checked</t>
+          <t>Multi-measure visuals 1.5, 1.6, 1.7 and narrative 1.8 checked</t>
         </is>
       </c>
       <c r="E63" s="47" t="inlineStr">
@@ -4311,8 +4319,10 @@
           <t>Doc 25 Table 3.7</t>
         </is>
       </c>
-      <c r="F63" s="52" t="n">
-        <v>7</v>
+      <c r="F63" s="52" t="inlineStr">
+        <is>
+          <t>7, 8</t>
+        </is>
       </c>
       <c r="G63" s="49">
         <f>IF($F63="","",IF(ISNUMBER(SEARCH(",",$F63)),"Yes — checks ","Yes — check ")&amp;$F63)</f>
@@ -4328,7 +4338,7 @@
       <c r="K63" s="22" t="n"/>
       <c r="L63" s="60" t="inlineStr">
         <is>
-          <t>V07</t>
+          <t>V07, V08</t>
         </is>
       </c>
     </row>
@@ -4372,7 +4382,7 @@
       <c r="J64" s="16" t="n"/>
       <c r="K64" s="15" t="n"/>
     </row>
-    <row r="65" ht="30" customHeight="1">
+    <row r="65" ht="70" customHeight="1">
       <c r="A65" s="44" t="inlineStr">
         <is>
           <t>G7</t>
@@ -4390,7 +4400,7 @@
       </c>
       <c r="D65" s="22" t="inlineStr">
         <is>
-          <t>Case visuals, baselines, Return Rows card and national-series narrative checked</t>
+          <t>Multi-measure, case and difference visuals, baselines, Return Rows card and national-series narrative checked</t>
         </is>
       </c>
       <c r="E65" s="47" t="inlineStr">
@@ -4400,7 +4410,7 @@
       </c>
       <c r="F65" s="52" t="inlineStr">
         <is>
-          <t>8, 9, 10, 11</t>
+          <t>7, 8, 9, 10, 11</t>
         </is>
       </c>
       <c r="G65" s="49">
@@ -4417,7 +4427,7 @@
       <c r="K65" s="22" t="n"/>
       <c r="L65" s="61" t="inlineStr">
         <is>
-          <t>V08, V09, V10, V11</t>
+          <t>V07, V08, V09, V10, V11</t>
         </is>
       </c>
     </row>
@@ -4510,7 +4520,7 @@
         </is>
       </c>
     </row>
-    <row r="68" ht="30" customHeight="1">
+    <row r="68" ht="70" customHeight="1">
       <c r="A68" s="38" t="inlineStr">
         <is>
           <t>G7</t>
@@ -4528,7 +4538,7 @@
       </c>
       <c r="D68" s="15" t="inlineStr">
         <is>
-          <t>Dual axis, case visuals, 2019 baselines checked</t>
+          <t>Dual axis, case visuals, item-type 2019 baselines 5.3, 5.6, 5.8 checked</t>
         </is>
       </c>
       <c r="E68" s="40" t="inlineStr">
@@ -4559,7 +4569,7 @@
         </is>
       </c>
     </row>
-    <row r="69" ht="30" customHeight="1">
+    <row r="69" ht="70" customHeight="1">
       <c r="A69" s="44" t="inlineStr">
         <is>
           <t>G7</t>
@@ -4577,7 +4587,7 @@
       </c>
       <c r="D69" s="22" t="inlineStr">
         <is>
-          <t>Slope visuals 6.8 and 6.9 carry Observation Count</t>
+          <t>Share Transfer 6.6 on one axis; slope visuals 6.8 and 6.9 carry Observation Count</t>
         </is>
       </c>
       <c r="E69" s="47" t="inlineStr">
@@ -4585,8 +4595,10 @@
           <t>Doc 25 Table 3.7</t>
         </is>
       </c>
-      <c r="F69" s="52" t="n">
-        <v>15</v>
+      <c r="F69" s="52" t="inlineStr">
+        <is>
+          <t>7, 15</t>
+        </is>
       </c>
       <c r="G69" s="49">
         <f>IF($F69="","",IF(ISNUMBER(SEARCH(",",$F69)),"Yes — checks ","Yes — check ")&amp;$F69)</f>
@@ -4602,7 +4614,7 @@
       <c r="K69" s="22" t="n"/>
       <c r="L69" s="60" t="inlineStr">
         <is>
-          <t>V15</t>
+          <t>V07, V15</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4658,7 @@
       <c r="J70" s="16" t="n"/>
       <c r="K70" s="15" t="n"/>
     </row>
-    <row r="71" ht="30" customHeight="1">
+    <row r="71" ht="70" customHeight="1">
       <c r="A71" s="44" t="inlineStr">
         <is>
           <t>G7</t>
@@ -4664,7 +4676,7 @@
       </c>
       <c r="D71" s="22" t="inlineStr">
         <is>
-          <t>Dual axis, case visuals, Pareto reaches the right edge</t>
+          <t>Dual axis, case and item-count visuals, Pareto reaches exactly 100%</t>
         </is>
       </c>
       <c r="E71" s="47" t="inlineStr">
@@ -4695,7 +4707,7 @@
         </is>
       </c>
     </row>
-    <row r="72" ht="30" customHeight="1">
+    <row r="72" ht="70" customHeight="1">
       <c r="A72" s="38" t="inlineStr">
         <is>
           <t>G7</t>
@@ -4713,7 +4725,7 @@
       </c>
       <c r="D72" s="15" t="inlineStr">
         <is>
-          <t>2017 cohort excluded or labelled on every survival visual</t>
+          <t>2017 cohort excluded or labelled on every visual 8.2–8.8; 8.6 on one axis; no dollar measure</t>
         </is>
       </c>
       <c r="E72" s="40" t="inlineStr">
@@ -4721,8 +4733,10 @@
           <t>Doc 25 Table 3.7</t>
         </is>
       </c>
-      <c r="F72" s="51" t="n">
-        <v>16</v>
+      <c r="F72" s="51" t="inlineStr">
+        <is>
+          <t>7, 8, 16</t>
+        </is>
       </c>
       <c r="G72" s="42">
         <f>IF($F72="","",IF(ISNUMBER(SEARCH(",",$F72)),"Yes — checks ","Yes — check ")&amp;$F72)</f>
@@ -4738,11 +4752,11 @@
       <c r="K72" s="15" t="n"/>
       <c r="L72" s="59" t="inlineStr">
         <is>
-          <t>V16</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="30" customHeight="1">
+          <t>V07, V08, V16</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="70" customHeight="1">
       <c r="A73" s="44" t="inlineStr">
         <is>
           <t>G7</t>
@@ -4760,7 +4774,7 @@
       </c>
       <c r="D73" s="22" t="inlineStr">
         <is>
-          <t>Dual axis and case visuals checked</t>
+          <t>Dual axis and case visuals 9.1–9.8 checked</t>
         </is>
       </c>
       <c r="E73" s="47" t="inlineStr">
@@ -4791,7 +4805,7 @@
         </is>
       </c>
     </row>
-    <row r="74" ht="30" customHeight="1">
+    <row r="74" ht="70" customHeight="1">
       <c r="A74" s="38" t="inlineStr">
         <is>
           <t>G7</t>
@@ -4809,7 +4823,7 @@
       </c>
       <c r="D74" s="15" t="inlineStr">
         <is>
-          <t>Case visual 10.5 checked</t>
+          <t>Adjusted vs Raw on one axis; case visuals 10.1–10.8 and method note checked</t>
         </is>
       </c>
       <c r="E74" s="40" t="inlineStr">
@@ -4817,8 +4831,10 @@
           <t>Doc 25 Table 3.7</t>
         </is>
       </c>
-      <c r="F74" s="51" t="n">
-        <v>8</v>
+      <c r="F74" s="51" t="inlineStr">
+        <is>
+          <t>7, 8</t>
+        </is>
       </c>
       <c r="G74" s="42">
         <f>IF($F74="","",IF(ISNUMBER(SEARCH(",",$F74)),"Yes — checks ","Yes — check ")&amp;$F74)</f>
@@ -4834,58 +4850,85 @@
       <c r="K74" s="15" t="n"/>
       <c r="L74" s="59" t="inlineStr">
         <is>
+          <t>V07, V08</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="29.5" customHeight="1">
+      <c r="A75" s="38" t="inlineStr">
+        <is>
+          <t>G7</t>
+        </is>
+      </c>
+      <c r="B75" s="39" t="inlineStr">
+        <is>
+          <t>G7.14</t>
+        </is>
+      </c>
+      <c r="C75" s="28" t="inlineStr">
+        <is>
+          <t>Drillthrough page built</t>
+        </is>
+      </c>
+      <c r="D75" s="15" t="inlineStr">
+        <is>
+          <t>Item Detail page carries cases only — no dollar measure</t>
+        </is>
+      </c>
+      <c r="E75" s="40" t="inlineStr">
+        <is>
+          <t>Doc 15 §8.3</t>
+        </is>
+      </c>
+      <c r="F75" s="51" t="n">
+        <v>8</v>
+      </c>
+      <c r="G75" s="42">
+        <f>IF($F75="","",IF(ISNUMBER(SEARCH(",",$F75)),"Yes — checks ","Yes — check ")&amp;$F75)</f>
+        <v/>
+      </c>
+      <c r="H75" s="17" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="I75" s="43" t="n"/>
+      <c r="J75" s="16" t="n"/>
+      <c r="K75" s="15" t="n"/>
+      <c r="L75" s="59" t="inlineStr">
+        <is>
           <t>V08</t>
         </is>
       </c>
     </row>
-    <row r="75" ht="20" customHeight="1">
-      <c r="A75" s="35" t="inlineStr">
-        <is>
-          <t>G8 — REPORT PASS   ·   Before publishing each report   ·   doc 25 §3.9</t>
-        </is>
-      </c>
-      <c r="B75" s="36" t="n"/>
-      <c r="C75" s="36" t="n"/>
-      <c r="D75" s="36" t="n"/>
-      <c r="E75" s="36" t="n"/>
-      <c r="F75" s="36" t="n"/>
-      <c r="G75" s="36" t="n"/>
-      <c r="H75" s="36" t="n"/>
-      <c r="I75" s="36" t="n"/>
-      <c r="J75" s="36" t="n"/>
-      <c r="K75" s="36" t="n"/>
-      <c r="L75" s="37" t="n"/>
-    </row>
-    <row r="76" ht="30" customHeight="1">
+    <row r="76" ht="29.5" customHeight="1">
       <c r="A76" s="38" t="inlineStr">
         <is>
-          <t>G8</t>
+          <t>G7</t>
         </is>
       </c>
       <c r="B76" s="39" t="inlineStr">
         <is>
-          <t>G8.01</t>
+          <t>G7.15</t>
         </is>
       </c>
       <c r="C76" s="28" t="inlineStr">
         <is>
-          <t>R1 report pass</t>
+          <t>Tooltip page built and assigned</t>
         </is>
       </c>
       <c r="D76" s="15" t="inlineStr">
         <is>
-          <t>Checks 7, 8, 15, 16, 17 recorded for R1; 9 and 11 updated from Page 3</t>
+          <t>Tooltip page shows cases only and is used on no dollar visual</t>
         </is>
       </c>
       <c r="E76" s="40" t="inlineStr">
         <is>
-          <t>Doc 15 §10</t>
-        </is>
-      </c>
-      <c r="F76" s="51" t="inlineStr">
-        <is>
-          <t>7, 8, 15, 16, 17</t>
-        </is>
+          <t>Doc 15 §8.4</t>
+        </is>
+      </c>
+      <c r="F76" s="51" t="n">
+        <v>8</v>
       </c>
       <c r="G76" s="42">
         <f>IF($F76="","",IF(ISNUMBER(SEARCH(",",$F76)),"Yes — checks ","Yes — check ")&amp;$F76)</f>
@@ -4899,83 +4942,80 @@
       <c r="I76" s="43" t="n"/>
       <c r="J76" s="16" t="n"/>
       <c r="K76" s="15" t="n"/>
-      <c r="L76" s="62" t="inlineStr">
-        <is>
-          <t>V07, V08, V15, V16, V17</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" ht="30" customHeight="1">
-      <c r="A77" s="44" t="inlineStr">
-        <is>
-          <t>G8</t>
-        </is>
-      </c>
-      <c r="B77" s="45" t="inlineStr">
-        <is>
-          <t>G8.02</t>
-        </is>
-      </c>
-      <c r="C77" s="46" t="inlineStr">
-        <is>
-          <t>R1 published</t>
-        </is>
-      </c>
-      <c r="D77" s="22" t="inlineStr">
-        <is>
-          <t>Published only with zero Blocking failures</t>
-        </is>
-      </c>
-      <c r="E77" s="47" t="inlineStr">
-        <is>
-          <t>Doc 15 §10</t>
-        </is>
-      </c>
-      <c r="F77" s="48" t="n"/>
-      <c r="G77" s="49">
+      <c r="L76" s="59" t="inlineStr">
+        <is>
+          <t>V08</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="43" customHeight="1">
+      <c r="A77" s="38" t="inlineStr">
+        <is>
+          <t>G7</t>
+        </is>
+      </c>
+      <c r="B77" s="39" t="inlineStr">
+        <is>
+          <t>G7.16</t>
+        </is>
+      </c>
+      <c r="C77" s="28" t="inlineStr">
+        <is>
+          <t>Cross-report wiring</t>
+        </is>
+      </c>
+      <c r="D77" s="15" t="inlineStr">
+        <is>
+          <t>Date slicer synced on every page, other slicers unsynced; Reset bookmark and button on every page; drillthrough from 3.6 opens Item Detail filtered</t>
+        </is>
+      </c>
+      <c r="E77" s="40" t="inlineStr">
+        <is>
+          <t>Doc 15 §8</t>
+        </is>
+      </c>
+      <c r="F77" s="51" t="n"/>
+      <c r="G77" s="42">
         <f>IF($F77="","",IF(ISNUMBER(SEARCH(",",$F77)),"Yes — checks ","Yes — check ")&amp;$F77)</f>
         <v/>
       </c>
-      <c r="H77" s="24" t="inlineStr">
+      <c r="H77" s="17" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
-      <c r="I77" s="50" t="n"/>
-      <c r="J77" s="23" t="n"/>
-      <c r="K77" s="22" t="n"/>
-    </row>
-    <row r="78" ht="30" customHeight="1">
+      <c r="I77" s="43" t="n"/>
+      <c r="J77" s="16" t="n"/>
+      <c r="K77" s="15" t="n"/>
+      <c r="L77" s="59" t="n"/>
+    </row>
+    <row r="78" ht="43" customHeight="1">
       <c r="A78" s="38" t="inlineStr">
         <is>
-          <t>G8</t>
+          <t>G7</t>
         </is>
       </c>
       <c r="B78" s="39" t="inlineStr">
         <is>
-          <t>G8.03</t>
+          <t>G7.17</t>
         </is>
       </c>
       <c r="C78" s="28" t="inlineStr">
         <is>
-          <t>R2 report pass</t>
+          <t>Accessibility pass</t>
         </is>
       </c>
       <c r="D78" s="15" t="inlineStr">
         <is>
-          <t>Checks 7, 8, 15, 16, 17 recorded for R2</t>
+          <t>Alt text, tab order, no meaning by colour alone, 4.5:1 text contrast, descriptive titles — on every page of each report</t>
         </is>
       </c>
       <c r="E78" s="40" t="inlineStr">
         <is>
-          <t>Doc 15 §10</t>
-        </is>
-      </c>
-      <c r="F78" s="51" t="inlineStr">
-        <is>
-          <t>7, 8, 15, 16, 17</t>
-        </is>
-      </c>
+          <t>Doc 15 §9</t>
+        </is>
+      </c>
+      <c r="F78" s="51" t="n"/>
       <c r="G78" s="42">
         <f>IF($F78="","",IF(ISNUMBER(SEARCH(",",$F78)),"Yes — checks ","Yes — check ")&amp;$F78)</f>
         <v/>
@@ -4988,81 +5028,55 @@
       <c r="I78" s="43" t="n"/>
       <c r="J78" s="16" t="n"/>
       <c r="K78" s="15" t="n"/>
-      <c r="L78" s="62" t="inlineStr">
-        <is>
-          <t>V07, V08, V15, V16, V17</t>
-        </is>
-      </c>
-    </row>
-    <row r="79" ht="30" customHeight="1">
-      <c r="A79" s="44" t="inlineStr">
+      <c r="L78" s="59" t="n"/>
+    </row>
+    <row r="79" ht="20" customHeight="1">
+      <c r="A79" s="35" t="inlineStr">
+        <is>
+          <t>G8 — REPORT PASS   ·   Before publishing each report   ·   doc 25 §3.9</t>
+        </is>
+      </c>
+      <c r="B79" s="36" t="n"/>
+      <c r="C79" s="36" t="n"/>
+      <c r="D79" s="36" t="n"/>
+      <c r="E79" s="36" t="n"/>
+      <c r="F79" s="36" t="n"/>
+      <c r="G79" s="36" t="n"/>
+      <c r="H79" s="36" t="n"/>
+      <c r="I79" s="36" t="n"/>
+      <c r="J79" s="36" t="n"/>
+      <c r="K79" s="36" t="n"/>
+      <c r="L79" s="37" t="n"/>
+    </row>
+    <row r="80" ht="70" customHeight="1">
+      <c r="A80" s="38" t="inlineStr">
         <is>
           <t>G8</t>
         </is>
       </c>
-      <c r="B79" s="45" t="inlineStr">
-        <is>
-          <t>G8.04</t>
-        </is>
-      </c>
-      <c r="C79" s="46" t="inlineStr">
-        <is>
-          <t>R2 published</t>
-        </is>
-      </c>
-      <c r="D79" s="22" t="inlineStr">
-        <is>
-          <t>Published only with zero Blocking failures</t>
-        </is>
-      </c>
-      <c r="E79" s="47" t="inlineStr">
+      <c r="B80" s="39" t="inlineStr">
+        <is>
+          <t>G8.01</t>
+        </is>
+      </c>
+      <c r="C80" s="28" t="inlineStr">
+        <is>
+          <t>R1 report pass</t>
+        </is>
+      </c>
+      <c r="D80" s="15" t="inlineStr">
+        <is>
+          <t>Checks 7, 8 and 17 recorded for R1 in doc 22 Reports covered; 9, 10 and 11 updated from Page 3</t>
+        </is>
+      </c>
+      <c r="E80" s="40" t="inlineStr">
         <is>
           <t>Doc 15 §10</t>
         </is>
       </c>
-      <c r="F79" s="48" t="n"/>
-      <c r="G79" s="49">
-        <f>IF($F79="","",IF(ISNUMBER(SEARCH(",",$F79)),"Yes — checks ","Yes — check ")&amp;$F79)</f>
-        <v/>
-      </c>
-      <c r="H79" s="24" t="inlineStr">
-        <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="I79" s="50" t="n"/>
-      <c r="J79" s="23" t="n"/>
-      <c r="K79" s="22" t="n"/>
-    </row>
-    <row r="80" ht="30" customHeight="1">
-      <c r="A80" s="38" t="inlineStr">
-        <is>
-          <t>G8</t>
-        </is>
-      </c>
-      <c r="B80" s="39" t="inlineStr">
-        <is>
-          <t>G8.05</t>
-        </is>
-      </c>
-      <c r="C80" s="28" t="inlineStr">
-        <is>
-          <t>R3 report pass</t>
-        </is>
-      </c>
-      <c r="D80" s="15" t="inlineStr">
-        <is>
-          <t>Checks 7, 8, 15, 16, 17 recorded for R3</t>
-        </is>
-      </c>
-      <c r="E80" s="40" t="inlineStr">
-        <is>
-          <t>Doc 15 §10</t>
-        </is>
-      </c>
       <c r="F80" s="51" t="inlineStr">
         <is>
-          <t>7, 8, 15, 16, 17</t>
+          <t>7, 8, 9, 10, 11, 17</t>
         </is>
       </c>
       <c r="G80" s="42">
@@ -5079,7 +5093,7 @@
       <c r="K80" s="15" t="n"/>
       <c r="L80" s="62" t="inlineStr">
         <is>
-          <t>V07, V08, V15, V16, V17</t>
+          <t>V07, V08, V09, V10, V11, V17</t>
         </is>
       </c>
     </row>
@@ -5091,12 +5105,12 @@
       </c>
       <c r="B81" s="45" t="inlineStr">
         <is>
-          <t>G8.06</t>
+          <t>G8.02</t>
         </is>
       </c>
       <c r="C81" s="46" t="inlineStr">
         <is>
-          <t>R3 published</t>
+          <t>R1 published</t>
         </is>
       </c>
       <c r="D81" s="22" t="inlineStr">
@@ -5123,7 +5137,7 @@
       <c r="J81" s="23" t="n"/>
       <c r="K81" s="22" t="n"/>
     </row>
-    <row r="82" ht="30" customHeight="1">
+    <row r="82" ht="70" customHeight="1">
       <c r="A82" s="38" t="inlineStr">
         <is>
           <t>G8</t>
@@ -5131,25 +5145,29 @@
       </c>
       <c r="B82" s="39" t="inlineStr">
         <is>
-          <t>G8.07</t>
+          <t>G8.03</t>
         </is>
       </c>
       <c r="C82" s="28" t="inlineStr">
         <is>
-          <t>Doc 22 Run 1 Outcome</t>
+          <t>R2 report pass</t>
         </is>
       </c>
       <c r="D82" s="15" t="inlineStr">
         <is>
-          <t>Reads PASS — all seventeen recorded</t>
+          <t>Checks 7, 8, 15 and 17 recorded for R2 in Reports covered; 9 updated from Page 2</t>
         </is>
       </c>
       <c r="E82" s="40" t="inlineStr">
         <is>
-          <t>Doc 22 Run Summary</t>
-        </is>
-      </c>
-      <c r="F82" s="41" t="n"/>
+          <t>Doc 15 §10</t>
+        </is>
+      </c>
+      <c r="F82" s="51" t="inlineStr">
+        <is>
+          <t>7, 8, 9, 15, 17</t>
+        </is>
+      </c>
       <c r="G82" s="42">
         <f>IF($F82="","",IF(ISNUMBER(SEARCH(",",$F82)),"Yes — checks ","Yes — check ")&amp;$F82)</f>
         <v/>
@@ -5162,52 +5180,83 @@
       <c r="I82" s="43" t="n"/>
       <c r="J82" s="16" t="n"/>
       <c r="K82" s="15" t="n"/>
-    </row>
-    <row r="83" ht="20" customHeight="1">
-      <c r="A83" s="35" t="inlineStr">
-        <is>
-          <t>G9 — PACKAGING   ·   Before the final push   ·   doc 25 §3.10</t>
-        </is>
-      </c>
-      <c r="B83" s="36" t="n"/>
-      <c r="C83" s="36" t="n"/>
-      <c r="D83" s="36" t="n"/>
-      <c r="E83" s="36" t="n"/>
-      <c r="F83" s="36" t="n"/>
-      <c r="G83" s="36" t="n"/>
-      <c r="H83" s="36" t="n"/>
-      <c r="I83" s="36" t="n"/>
-      <c r="J83" s="36" t="n"/>
-      <c r="K83" s="36" t="n"/>
-      <c r="L83" s="37" t="n"/>
-    </row>
-    <row r="84" ht="30" customHeight="1">
+      <c r="L82" s="62" t="inlineStr">
+        <is>
+          <t>V07, V08, V09, V15, V17</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="30" customHeight="1">
+      <c r="A83" s="44" t="inlineStr">
+        <is>
+          <t>G8</t>
+        </is>
+      </c>
+      <c r="B83" s="45" t="inlineStr">
+        <is>
+          <t>G8.04</t>
+        </is>
+      </c>
+      <c r="C83" s="46" t="inlineStr">
+        <is>
+          <t>R2 published</t>
+        </is>
+      </c>
+      <c r="D83" s="22" t="inlineStr">
+        <is>
+          <t>Published only with zero Blocking failures</t>
+        </is>
+      </c>
+      <c r="E83" s="47" t="inlineStr">
+        <is>
+          <t>Doc 15 §10</t>
+        </is>
+      </c>
+      <c r="F83" s="48" t="n"/>
+      <c r="G83" s="49">
+        <f>IF($F83="","",IF(ISNUMBER(SEARCH(",",$F83)),"Yes — checks ","Yes — check ")&amp;$F83)</f>
+        <v/>
+      </c>
+      <c r="H83" s="24" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="I83" s="50" t="n"/>
+      <c r="J83" s="23" t="n"/>
+      <c r="K83" s="22" t="n"/>
+    </row>
+    <row r="84" ht="70" customHeight="1">
       <c r="A84" s="38" t="inlineStr">
         <is>
-          <t>G9</t>
+          <t>G8</t>
         </is>
       </c>
       <c r="B84" s="39" t="inlineStr">
         <is>
-          <t>G9.01</t>
+          <t>G8.05</t>
         </is>
       </c>
       <c r="C84" s="28" t="inlineStr">
         <is>
-          <t>Doc 00 §14 checklist</t>
+          <t>R3 report pass</t>
         </is>
       </c>
       <c r="D84" s="15" t="inlineStr">
         <is>
-          <t>Run end to end</t>
+          <t>Checks 7, 8, 16 and 17 recorded for R3 in Reports covered; 14 updated from Page 1</t>
         </is>
       </c>
       <c r="E84" s="40" t="inlineStr">
         <is>
-          <t>Doc 00 §14</t>
-        </is>
-      </c>
-      <c r="F84" s="41" t="n"/>
+          <t>Doc 15 §10</t>
+        </is>
+      </c>
+      <c r="F84" s="51" t="inlineStr">
+        <is>
+          <t>7, 8, 14, 16, 17</t>
+        </is>
+      </c>
       <c r="G84" s="42">
         <f>IF($F84="","",IF(ISNUMBER(SEARCH(",",$F84)),"Yes — checks ","Yes — check ")&amp;$F84)</f>
         <v/>
@@ -5220,31 +5269,36 @@
       <c r="I84" s="43" t="n"/>
       <c r="J84" s="16" t="n"/>
       <c r="K84" s="15" t="n"/>
+      <c r="L84" s="62" t="inlineStr">
+        <is>
+          <t>V07, V08, V14, V16, V17</t>
+        </is>
+      </c>
     </row>
     <row r="85" ht="30" customHeight="1">
       <c r="A85" s="44" t="inlineStr">
         <is>
-          <t>G9</t>
+          <t>G8</t>
         </is>
       </c>
       <c r="B85" s="45" t="inlineStr">
         <is>
-          <t>G9.02</t>
+          <t>G8.06</t>
         </is>
       </c>
       <c r="C85" s="46" t="inlineStr">
         <is>
-          <t>Repository search</t>
+          <t>R3 published</t>
         </is>
       </c>
       <c r="D85" s="22" t="inlineStr">
         <is>
-          <t>No .csv, no key=, no first six characters of the key</t>
+          <t>Published only with zero Blocking failures</t>
         </is>
       </c>
       <c r="E85" s="47" t="inlineStr">
         <is>
-          <t>Doc 00 §12, §14</t>
+          <t>Doc 15 §10</t>
         </is>
       </c>
       <c r="F85" s="48" t="n"/>
@@ -5261,30 +5315,30 @@
       <c r="J85" s="23" t="n"/>
       <c r="K85" s="22" t="n"/>
     </row>
-    <row r="86" ht="30" customHeight="1">
+    <row r="86" ht="70" customHeight="1">
       <c r="A86" s="38" t="inlineStr">
         <is>
-          <t>G9</t>
+          <t>G8</t>
         </is>
       </c>
       <c r="B86" s="39" t="inlineStr">
         <is>
-          <t>G9.03</t>
+          <t>G8.07</t>
         </is>
       </c>
       <c r="C86" s="28" t="inlineStr">
         <is>
-          <t>Report PBIP folders</t>
+          <t>Doc 22 Run 1 Outcome</t>
         </is>
       </c>
       <c r="D86" s="15" t="inlineStr">
         <is>
-          <t>Report definition only, no TMDL — the reports are thin</t>
+          <t>Reads PASS — all seventeen recorded (PASSED WITH FAILURES only with a logged Advisory failure)</t>
         </is>
       </c>
       <c r="E86" s="40" t="inlineStr">
         <is>
-          <t>Doc 00 §14</t>
+          <t>Doc 22 Run Summary</t>
         </is>
       </c>
       <c r="F86" s="41" t="n"/>
@@ -5301,69 +5355,143 @@
       <c r="J86" s="16" t="n"/>
       <c r="K86" s="15" t="n"/>
     </row>
-    <row r="87">
-      <c r="A87" s="53" t="n"/>
-      <c r="B87" s="53" t="n"/>
-      <c r="C87" s="53" t="n"/>
-      <c r="D87" s="53" t="n"/>
-      <c r="E87" s="53" t="n"/>
-      <c r="F87" s="53" t="n"/>
-      <c r="G87" s="42">
-        <f>IF($F87="","",IF(ISNUMBER(SEARCH(",",$F87)),"Yes — checks ","Yes — check ")&amp;$F87)</f>
-        <v/>
-      </c>
-      <c r="H87" s="53" t="n"/>
-      <c r="I87" s="54" t="n"/>
-      <c r="J87" s="53" t="n"/>
-      <c r="K87" s="53" t="n"/>
-    </row>
-    <row r="88">
-      <c r="A88" s="53" t="n"/>
-      <c r="B88" s="53" t="n"/>
-      <c r="C88" s="53" t="n"/>
-      <c r="D88" s="53" t="n"/>
-      <c r="E88" s="53" t="n"/>
-      <c r="F88" s="53" t="n"/>
+    <row r="87" ht="20" customHeight="1">
+      <c r="A87" s="35" t="inlineStr">
+        <is>
+          <t>G9 — PACKAGING   ·   Before the final push   ·   doc 25 §3.10</t>
+        </is>
+      </c>
+      <c r="B87" s="36" t="n"/>
+      <c r="C87" s="36" t="n"/>
+      <c r="D87" s="36" t="n"/>
+      <c r="E87" s="36" t="n"/>
+      <c r="F87" s="36" t="n"/>
+      <c r="G87" s="36" t="n"/>
+      <c r="H87" s="36" t="n"/>
+      <c r="I87" s="36" t="n"/>
+      <c r="J87" s="36" t="n"/>
+      <c r="K87" s="36" t="n"/>
+      <c r="L87" s="37" t="n"/>
+    </row>
+    <row r="88" ht="30" customHeight="1">
+      <c r="A88" s="38" t="inlineStr">
+        <is>
+          <t>G9</t>
+        </is>
+      </c>
+      <c r="B88" s="39" t="inlineStr">
+        <is>
+          <t>G9.01</t>
+        </is>
+      </c>
+      <c r="C88" s="28" t="inlineStr">
+        <is>
+          <t>Doc 00 §14 checklist</t>
+        </is>
+      </c>
+      <c r="D88" s="15" t="inlineStr">
+        <is>
+          <t>Run end to end</t>
+        </is>
+      </c>
+      <c r="E88" s="40" t="inlineStr">
+        <is>
+          <t>Doc 00 §14</t>
+        </is>
+      </c>
+      <c r="F88" s="41" t="n"/>
       <c r="G88" s="42">
         <f>IF($F88="","",IF(ISNUMBER(SEARCH(",",$F88)),"Yes — checks ","Yes — check ")&amp;$F88)</f>
         <v/>
       </c>
-      <c r="H88" s="53" t="n"/>
-      <c r="I88" s="54" t="n"/>
-      <c r="J88" s="53" t="n"/>
-      <c r="K88" s="53" t="n"/>
-    </row>
-    <row r="89">
-      <c r="A89" s="53" t="n"/>
-      <c r="B89" s="53" t="n"/>
-      <c r="C89" s="53" t="n"/>
-      <c r="D89" s="53" t="n"/>
-      <c r="E89" s="53" t="n"/>
-      <c r="F89" s="53" t="n"/>
-      <c r="G89" s="42">
+      <c r="H88" s="17" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="I88" s="43" t="n"/>
+      <c r="J88" s="16" t="n"/>
+      <c r="K88" s="15" t="n"/>
+    </row>
+    <row r="89" ht="30" customHeight="1">
+      <c r="A89" s="44" t="inlineStr">
+        <is>
+          <t>G9</t>
+        </is>
+      </c>
+      <c r="B89" s="45" t="inlineStr">
+        <is>
+          <t>G9.02</t>
+        </is>
+      </c>
+      <c r="C89" s="46" t="inlineStr">
+        <is>
+          <t>Repository search</t>
+        </is>
+      </c>
+      <c r="D89" s="22" t="inlineStr">
+        <is>
+          <t>No .csv, no key=, no first six characters of the key</t>
+        </is>
+      </c>
+      <c r="E89" s="47" t="inlineStr">
+        <is>
+          <t>Doc 00 §12, §14</t>
+        </is>
+      </c>
+      <c r="F89" s="48" t="n"/>
+      <c r="G89" s="49">
         <f>IF($F89="","",IF(ISNUMBER(SEARCH(",",$F89)),"Yes — checks ","Yes — check ")&amp;$F89)</f>
         <v/>
       </c>
-      <c r="H89" s="53" t="n"/>
-      <c r="I89" s="54" t="n"/>
-      <c r="J89" s="53" t="n"/>
-      <c r="K89" s="53" t="n"/>
-    </row>
-    <row r="90">
-      <c r="A90" s="53" t="n"/>
-      <c r="B90" s="53" t="n"/>
-      <c r="C90" s="53" t="n"/>
-      <c r="D90" s="53" t="n"/>
-      <c r="E90" s="53" t="n"/>
-      <c r="F90" s="53" t="n"/>
+      <c r="H89" s="24" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="I89" s="50" t="n"/>
+      <c r="J89" s="23" t="n"/>
+      <c r="K89" s="22" t="n"/>
+    </row>
+    <row r="90" ht="30" customHeight="1">
+      <c r="A90" s="38" t="inlineStr">
+        <is>
+          <t>G9</t>
+        </is>
+      </c>
+      <c r="B90" s="39" t="inlineStr">
+        <is>
+          <t>G9.03</t>
+        </is>
+      </c>
+      <c r="C90" s="28" t="inlineStr">
+        <is>
+          <t>Report PBIP folders</t>
+        </is>
+      </c>
+      <c r="D90" s="15" t="inlineStr">
+        <is>
+          <t>Report definition only, no TMDL — the reports are thin</t>
+        </is>
+      </c>
+      <c r="E90" s="40" t="inlineStr">
+        <is>
+          <t>Doc 00 §14</t>
+        </is>
+      </c>
+      <c r="F90" s="41" t="n"/>
       <c r="G90" s="42">
         <f>IF($F90="","",IF(ISNUMBER(SEARCH(",",$F90)),"Yes — checks ","Yes — check ")&amp;$F90)</f>
         <v/>
       </c>
-      <c r="H90" s="53" t="n"/>
-      <c r="I90" s="54" t="n"/>
-      <c r="J90" s="53" t="n"/>
-      <c r="K90" s="53" t="n"/>
+      <c r="H90" s="17" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="I90" s="43" t="n"/>
+      <c r="J90" s="16" t="n"/>
+      <c r="K90" s="15" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="53" t="n"/>
@@ -13525,23 +13653,87 @@
       <c r="J600" s="53" t="n"/>
       <c r="K600" s="53" t="n"/>
     </row>
+    <row r="601">
+      <c r="A601" s="53" t="n"/>
+      <c r="B601" s="53" t="n"/>
+      <c r="C601" s="53" t="n"/>
+      <c r="D601" s="53" t="n"/>
+      <c r="E601" s="53" t="n"/>
+      <c r="F601" s="53" t="n"/>
+      <c r="G601" s="42">
+        <f>IF($F601="","",IF(ISNUMBER(SEARCH(",",$F601)),"Yes — checks ","Yes — check ")&amp;$F601)</f>
+        <v/>
+      </c>
+      <c r="H601" s="53" t="n"/>
+      <c r="I601" s="54" t="n"/>
+      <c r="J601" s="53" t="n"/>
+      <c r="K601" s="53" t="n"/>
+    </row>
+    <row r="602">
+      <c r="A602" s="53" t="n"/>
+      <c r="B602" s="53" t="n"/>
+      <c r="C602" s="53" t="n"/>
+      <c r="D602" s="53" t="n"/>
+      <c r="E602" s="53" t="n"/>
+      <c r="F602" s="53" t="n"/>
+      <c r="G602" s="42">
+        <f>IF($F602="","",IF(ISNUMBER(SEARCH(",",$F602)),"Yes — checks ","Yes — check ")&amp;$F602)</f>
+        <v/>
+      </c>
+      <c r="H602" s="53" t="n"/>
+      <c r="I602" s="54" t="n"/>
+      <c r="J602" s="53" t="n"/>
+      <c r="K602" s="53" t="n"/>
+    </row>
+    <row r="603">
+      <c r="A603" s="53" t="n"/>
+      <c r="B603" s="53" t="n"/>
+      <c r="C603" s="53" t="n"/>
+      <c r="D603" s="53" t="n"/>
+      <c r="E603" s="53" t="n"/>
+      <c r="F603" s="53" t="n"/>
+      <c r="G603" s="42">
+        <f>IF($F603="","",IF(ISNUMBER(SEARCH(",",$F603)),"Yes — checks ","Yes — check ")&amp;$F603)</f>
+        <v/>
+      </c>
+      <c r="H603" s="53" t="n"/>
+      <c r="I603" s="54" t="n"/>
+      <c r="J603" s="53" t="n"/>
+      <c r="K603" s="53" t="n"/>
+    </row>
+    <row r="604">
+      <c r="A604" s="53" t="n"/>
+      <c r="B604" s="53" t="n"/>
+      <c r="C604" s="53" t="n"/>
+      <c r="D604" s="53" t="n"/>
+      <c r="E604" s="53" t="n"/>
+      <c r="F604" s="53" t="n"/>
+      <c r="G604" s="42">
+        <f>IF($F604="","",IF(ISNUMBER(SEARCH(",",$F604)),"Yes — checks ","Yes — check ")&amp;$F604)</f>
+        <v/>
+      </c>
+      <c r="H604" s="53" t="n"/>
+      <c r="I604" s="54" t="n"/>
+      <c r="J604" s="53" t="n"/>
+      <c r="K604" s="53" t="n"/>
+    </row>
   </sheetData>
   <autoFilter ref="A4:L600"/>
   <mergeCells count="12">
+    <mergeCell ref="A30:L30"/>
+    <mergeCell ref="A2:L2"/>
     <mergeCell ref="A25:L25"/>
     <mergeCell ref="A41:L41"/>
-    <mergeCell ref="A75:L75"/>
+    <mergeCell ref="A5:L5"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A55:L55"/>
+    <mergeCell ref="A61:L61"/>
+    <mergeCell ref="A9:L9"/>
+    <mergeCell ref="A79:L79"/>
     <mergeCell ref="A18:L18"/>
-    <mergeCell ref="A9:L9"/>
-    <mergeCell ref="A55:L55"/>
-    <mergeCell ref="A83:L83"/>
-    <mergeCell ref="A30:L30"/>
-    <mergeCell ref="A2:L2"/>
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="A5:L5"/>
-    <mergeCell ref="A61:L61"/>
+    <mergeCell ref="A87:L87"/>
   </mergeCells>
-  <conditionalFormatting sqref="H5:H600">
+  <conditionalFormatting sqref="H5:H604">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"Pass"</formula>
     </cfRule>
@@ -13556,10 +13748,10 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation sqref="H5:H600" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Result" error="Pass, Fail, N/A or Not run" type="list">
+    <dataValidation sqref="H5:H604" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Result" error="Pass, Fail, N/A or Not run" type="list">
       <formula1>"Pass,Fail,N/A,Not run"</formula1>
     </dataValidation>
-    <dataValidation sqref="A5:A600" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="A5:A604" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"G0,G1,G2,G3,G4,G5,G6,G7,G8,G9"</formula1>
     </dataValidation>
   </dataValidations>
@@ -18730,7 +18922,7 @@
   </conditionalFormatting>
   <dataValidations count="2">
     <dataValidation sqref="B5:B300" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=Triggers!$A$5:$A$13</formula1>
+      <formula1>=Triggers!$A$5:$A$15</formula1>
     </dataValidation>
     <dataValidation sqref="F5:F300" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Pass,Fail,N/A,Not run"</formula1>
@@ -18747,7 +18939,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -18769,6 +18961,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="32" customHeight="1">
       <c r="A4" s="34" t="inlineStr">
         <is>
@@ -18936,6 +19129,40 @@
       <c r="C13" s="56" t="inlineStr">
         <is>
           <t>Not recorded in doc 22</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="16" customHeight="1">
+      <c r="A14" s="28" t="inlineStr">
+        <is>
+          <t>A sql/04, 05 or 06 script is edited</t>
+        </is>
+      </c>
+      <c r="B14" s="55" t="inlineStr">
+        <is>
+          <t>sql/04 to 06 in order; checks 1, 12 and 13; then the rest of the twelve data checks</t>
+        </is>
+      </c>
+      <c r="C14" s="56" t="inlineStr">
+        <is>
+          <t>Ad hoc</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="29.5" customHeight="1">
+      <c r="A15" s="28" t="inlineStr">
+        <is>
+          <t>A Power Query source query or parameter is edited</t>
+        </is>
+      </c>
+      <c r="B15" s="55" t="inlineStr">
+        <is>
+          <t>Checks 2, 4 and 6; then 3 and 5</t>
+        </is>
+      </c>
+      <c r="C15" s="56" t="inlineStr">
+        <is>
+          <t>Ad hoc</t>
         </is>
       </c>
     </row>
